--- a/data/trans_dic/P36$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,18</t>
+          <t>0,39; 2,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,77</t>
+          <t>2,02; 6,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,76</t>
+          <t>0,76; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,15</t>
+          <t>0,5; 2,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,37</t>
+          <t>1,52; 4,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,14</t>
+          <t>0,45; 2,02</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,32</t>
+          <t>1,09; 4,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,77</t>
+          <t>0,21; 3,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,3</t>
+          <t>0,55; 3,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,28</t>
+          <t>0,51; 3,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,19</t>
+          <t>1,08; 3,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,41</t>
+          <t>0,5; 2,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,04</t>
+          <t>1,36; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,37</t>
+          <t>1,15; 3,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,72</t>
+          <t>0,55; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,56</t>
+          <t>0,61; 6,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,23</t>
+          <t>0,36; 3,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,72</t>
+          <t>1,42; 3,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,86</t>
+          <t>1,1; 3,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,5</t>
+          <t>0,6; 2,55</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,83</t>
+          <t>1,25; 2,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,33</t>
+          <t>2,07; 4,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,95</t>
+          <t>1,15; 2,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,09</t>
+          <t>1,02; 3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,06</t>
+          <t>1,48; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,72</t>
+          <t>0,86; 2,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,69</t>
+          <t>1,33; 2,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,73</t>
+          <t>2,12; 3,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,4</t>
+          <t>1,21; 2,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,11</t>
+          <t>2,06; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,66</t>
+          <t>1,51; 4,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,71</t>
+          <t>1,73; 4,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,17</t>
+          <t>0,84; 3,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,51</t>
+          <t>0,26; 1,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,61</t>
+          <t>0,25; 1,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,85</t>
+          <t>1,62; 3,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,37</t>
+          <t>0,87; 2,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,64</t>
+          <t>1,13; 2,74</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,28</t>
+          <t>0,3; 2,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,29</t>
+          <t>1,08; 5,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,97</t>
+          <t>1,44; 5,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,19</t>
+          <t>0,84; 2,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,2</t>
+          <t>1,4; 3,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,95</t>
+          <t>0,65; 2,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,04</t>
+          <t>0,81; 1,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,23</t>
+          <t>1,62; 3,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,34</t>
+          <t>1,02; 2,36</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,54</t>
+          <t>1,6; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,29</t>
+          <t>2,03; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,06</t>
+          <t>1,2; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,22</t>
+          <t>1,26; 2,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,36</t>
+          <t>0,7; 1,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,17</t>
+          <t>1,51; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,57</t>
+          <t>1,8; 2,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,74</t>
+          <t>1,16; 1,74</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2481; 10294</t>
+          <t>1842; 10228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9274; 29603</t>
+          <t>8847; 27595</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3171; 16145</t>
+          <t>3263; 15866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1144; 9409</t>
+          <t>1139; 9404</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>966; 8202</t>
+          <t>973; 8214</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4161; 16778</t>
+          <t>3907; 15686</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11993; 32762</t>
+          <t>11404; 32171</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3178; 16628</t>
+          <t>3531; 15670</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4413; 15768</t>
+          <t>3963; 16446</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>896; 11527</t>
+          <t>893; 12514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4381</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2043; 12246</t>
+          <t>2039; 11399</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1708; 11087</t>
+          <t>1737; 12469</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6747</t>
+          <t>0; 6667</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7812; 23495</t>
+          <t>7948; 22537</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3823; 18160</t>
+          <t>3779; 18536</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>868; 7534</t>
+          <t>867; 7554</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7411; 21838</t>
+          <t>7352; 22720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6696; 21132</t>
+          <t>7219; 21080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2051; 14142</t>
+          <t>2884; 14878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1012; 9331</t>
+          <t>1025; 10166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>942; 8402</t>
+          <t>933; 8949</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6218</t>
+          <t>0; 6424</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10133; 26350</t>
+          <t>10038; 26918</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9341; 25361</t>
+          <t>9767; 26837</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3905; 17159</t>
+          <t>4088; 17526</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15714; 34955</t>
+          <t>15433; 35967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23451; 50085</t>
+          <t>23931; 48702</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13595; 33865</t>
+          <t>13207; 34160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6694; 22023</t>
+          <t>7265; 22885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11349; 31028</t>
+          <t>11319; 30637</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7232; 22448</t>
+          <t>7087; 21212</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27275; 52372</t>
+          <t>26015; 50611</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39761; 71770</t>
+          <t>40800; 72373</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23356; 47437</t>
+          <t>23890; 48449</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6936; 21405</t>
+          <t>7229; 21320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7243; 23734</t>
+          <t>7683; 24159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10702; 29130</t>
+          <t>10719; 28794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4959; 17967</t>
+          <t>4753; 17119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2015; 11425</t>
+          <t>2007; 11332</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1823; 11911</t>
+          <t>1856; 10988</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14861; 35352</t>
+          <t>14901; 33573</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11334; 30019</t>
+          <t>11066; 30455</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14984; 35878</t>
+          <t>15329; 37155</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>918; 9792</t>
+          <t>903; 7925</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3166; 14106</t>
+          <t>2887; 15010</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4718; 17152</t>
+          <t>4137; 16036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10804; 27346</t>
+          <t>10509; 28650</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16017; 35469</t>
+          <t>15585; 34880</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6811; 21080</t>
+          <t>7010; 22339</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13201; 31593</t>
+          <t>12591; 30767</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21232; 44389</t>
+          <t>22294; 45264</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13898; 32048</t>
+          <t>13991; 32197</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51134; 82824</t>
+          <t>52340; 86228</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69439; 112502</t>
+          <t>69448; 111638</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48823; 82355</t>
+          <t>48541; 82448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39689; 69555</t>
+          <t>40648; 69094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46181; 78728</t>
+          <t>44518; 77859</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23999; 48076</t>
+          <t>24766; 48839</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>101680; 144072</t>
+          <t>100276; 143700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125414; 178554</t>
+          <t>125291; 177311</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79412; 120574</t>
+          <t>79910; 120031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$nada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Clase-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,16</t>
+          <t>0,52; 2,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,31</t>
+          <t>2,15; 6,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,7</t>
+          <t>0,75; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,07</t>
+          <t>0,37; 3,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,62</t>
+          <t>0,31; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,01</t>
+          <t>0,49; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,29</t>
+          <t>1,53; 4,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,02</t>
+          <t>0,41; 2,05</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,5</t>
+          <t>1,18; 4,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,0</t>
+          <t>0,21; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,07</t>
+          <t>0,56; 3,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,69</t>
+          <t>0,53; 3,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,06</t>
+          <t>1,13; 3,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,01</t>
+          <t>0,12; 1,09</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,2</t>
+          <t>1,34; 4,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,36</t>
+          <t>1,11; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,86</t>
+          <t>0,4; 2,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,06</t>
+          <t>0,67; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,44</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,8</t>
+          <t>1,47; 3,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,02</t>
+          <t>1,06; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,55</t>
+          <t>0,57; 2,58</t>
         </is>
       </c>
     </row>
@@ -1008,42 +1008,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,91</t>
+          <t>1,31; 2,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,21</t>
+          <t>2,01; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,97</t>
+          <t>1,18; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,21</t>
+          <t>1,03; 3,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,01</t>
+          <t>1,51; 3,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,57</t>
+          <t>0,91; 2,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,6</t>
+          <t>1,34; 2,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,76</t>
+          <t>2,04; 3,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,08</t>
+          <t>2,08; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,74</t>
+          <t>1,54; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,65</t>
+          <t>1,77; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,02</t>
+          <t>0,83; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,49</t>
+          <t>0,27; 1,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,49</t>
+          <t>0,25; 1,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,66</t>
+          <t>1,63; 3,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,4</t>
+          <t>0,86; 2,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,74</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,66</t>
+          <t>0,31; 2,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,62</t>
+          <t>1,1; 5,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,58</t>
+          <t>1,69; 5,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,29</t>
+          <t>0,91; 2,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,14</t>
+          <t>1,44; 3,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,07</t>
+          <t>0,6; 2,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,99</t>
+          <t>0,82; 1,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,29</t>
+          <t>1,61; 3,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,36</t>
+          <t>1,03; 2,4</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,64</t>
+          <t>1,64; 2,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,27</t>
+          <t>2,04; 3,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,44</t>
+          <t>1,43; 2,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,05</t>
+          <t>1,18; 2,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,2</t>
+          <t>1,28; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,38</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,16</t>
+          <t>1,53; 2,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,55</t>
+          <t>1,82; 2,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,74</t>
+          <t>1,17; 1,74</t>
         </is>
       </c>
     </row>
@@ -1639,27 +1639,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1842; 10228</t>
+          <t>2475; 11293</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8847; 27595</t>
+          <t>9402; 29170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3263; 15866</t>
+          <t>3209; 15903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1139; 9404</t>
+          <t>1145; 10814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>973; 8214</t>
+          <t>960; 8406</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3907; 15686</t>
+          <t>3816; 15484</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11404; 32171</t>
+          <t>11505; 32534</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3531; 15670</t>
+          <t>3205; 15897</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3963; 16446</t>
+          <t>4326; 15646</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>893; 12514</t>
+          <t>891; 10584</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2039; 11399</t>
+          <t>2065; 12522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1737; 12469</t>
+          <t>1785; 12165</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6667</t>
+          <t>0; 6153</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7948; 22537</t>
+          <t>8303; 24033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3779; 18536</t>
+          <t>3720; 17664</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>867; 7554</t>
+          <t>869; 8161</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7352; 22720</t>
+          <t>7256; 22018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7219; 21080</t>
+          <t>6979; 21022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2884; 14878</t>
+          <t>2075; 13982</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1025; 10166</t>
+          <t>1130; 10270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>933; 8949</t>
+          <t>948; 8973</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6424</t>
+          <t>0; 6431</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10038; 26918</t>
+          <t>10414; 26667</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9767; 26837</t>
+          <t>9439; 25374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4088; 17526</t>
+          <t>3948; 17705</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15433; 35967</t>
+          <t>16239; 35325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23931; 48702</t>
+          <t>23307; 48879</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13207; 34160</t>
+          <t>13570; 33605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7265; 22885</t>
+          <t>7376; 22952</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11319; 30637</t>
+          <t>11513; 30388</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7087; 21212</t>
+          <t>7497; 23184</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26015; 50611</t>
+          <t>26035; 51187</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40800; 72373</t>
+          <t>39241; 72903</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23890; 48449</t>
+          <t>23926; 48309</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7229; 21320</t>
+          <t>7306; 21867</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7683; 24159</t>
+          <t>7829; 24984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10719; 28794</t>
+          <t>10958; 29809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4753; 17119</t>
+          <t>4718; 17678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2007; 11332</t>
+          <t>2023; 12312</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1856; 10988</t>
+          <t>1838; 10871</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14901; 33573</t>
+          <t>14948; 32479</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11066; 30455</t>
+          <t>10897; 30688</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15329; 37155</t>
+          <t>15545; 36937</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>903; 7925</t>
+          <t>910; 8036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2887; 15010</t>
+          <t>2923; 14482</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4137; 16036</t>
+          <t>4848; 16486</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10509; 28650</t>
+          <t>11320; 28373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15585; 34880</t>
+          <t>15947; 34944</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7010; 22339</t>
+          <t>6438; 21882</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12591; 30767</t>
+          <t>12740; 30529</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22294; 45264</t>
+          <t>22165; 45039</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13991; 32197</t>
+          <t>14039; 32793</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>52340; 86228</t>
+          <t>53365; 85231</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69448; 111638</t>
+          <t>69816; 110814</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48541; 82448</t>
+          <t>48412; 83457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40648; 69094</t>
+          <t>39960; 69811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44518; 77859</t>
+          <t>45429; 78681</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24766; 48839</t>
+          <t>24690; 47659</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100276; 143700</t>
+          <t>101330; 144384</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125291; 177311</t>
+          <t>126487; 176231</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79910; 120031</t>
+          <t>80605; 120573</t>
         </is>
       </c>
     </row>
